--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.1674215923268</v>
+        <v>7.664706008753105</v>
       </c>
       <c r="D2" t="n">
-        <v>22.23610677354389</v>
+        <v>3.613367350700882</v>
       </c>
       <c r="E2" t="n">
-        <v>10.49392732895159</v>
+        <v>1.705263190954634</v>
       </c>
       <c r="F2" t="n">
-        <v>11.62438628426152</v>
+        <v>1.888962771192497</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.77838343801677</v>
+        <v>5.326487308677725</v>
       </c>
       <c r="D3" t="n">
-        <v>33.89515248803739</v>
+        <v>5.507962279306076</v>
       </c>
       <c r="E3" t="n">
-        <v>10.49392732895159</v>
+        <v>1.705263190954634</v>
       </c>
       <c r="F3" t="n">
-        <v>11.62438628426152</v>
+        <v>1.888962771192497</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.66195471812148</v>
+        <v>5.79506764169474</v>
       </c>
       <c r="D4" t="n">
-        <v>16.35076439541879</v>
+        <v>2.656999214255553</v>
       </c>
       <c r="E4" t="n">
-        <v>10.49392732895159</v>
+        <v>1.705263190954634</v>
       </c>
       <c r="F4" t="n">
-        <v>11.62438628426152</v>
+        <v>1.888962771192497</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.09565080560734</v>
+        <v>5.053043255911192</v>
       </c>
       <c r="D5" t="n">
-        <v>8.079516780214721</v>
+        <v>1.312921476784892</v>
       </c>
       <c r="E5" t="n">
-        <v>10.49392732895159</v>
+        <v>1.705263190954634</v>
       </c>
       <c r="F5" t="n">
-        <v>11.62438628426152</v>
+        <v>1.888962771192497</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.45262321261976</v>
+        <v>9.336051272050712</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>0.56875</v>
       </c>
       <c r="E6" t="n">
-        <v>10.49392732895159</v>
+        <v>1.705263190954634</v>
       </c>
       <c r="F6" t="n">
-        <v>11.62438628426152</v>
+        <v>1.888962771192497</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.10496008479277</v>
+        <v>5.867056013778826</v>
       </c>
       <c r="D7" t="n">
-        <v>37.59558685814218</v>
+        <v>6.109282864448105</v>
       </c>
       <c r="E7" t="n">
-        <v>10.49392732895159</v>
+        <v>1.705263190954634</v>
       </c>
       <c r="F7" t="n">
-        <v>11.62438628426152</v>
+        <v>1.888962771192497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.98323079554309</v>
+        <v>3.734775004275753</v>
       </c>
       <c r="D8" t="n">
-        <v>23.85809940574399</v>
+        <v>3.876941153433398</v>
       </c>
       <c r="E8" t="n">
-        <v>10.49392732895159</v>
+        <v>1.705263190954634</v>
       </c>
       <c r="F8" t="n">
-        <v>11.62438628426152</v>
+        <v>1.888962771192497</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
